--- a/artfynd/A 19676-2024 artfynd.xlsx
+++ b/artfynd/A 19676-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>90428543</v>
       </c>
       <c r="B2" t="n">
-        <v>103088</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105428</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>319939.4536667911</v>
+        <v>319939</v>
       </c>
       <c r="R2" t="n">
-        <v>6469056.068328692</v>
+        <v>6469056</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -748,19 +743,9 @@
           <t>2002-07-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2002-07-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -804,12 +789,7 @@
         <v>90428547</v>
       </c>
       <c r="B3" t="n">
-        <v>104654</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107061</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>319939.4536667911</v>
+        <v>319939</v>
       </c>
       <c r="R3" t="n">
-        <v>6469056.068328692</v>
+        <v>6469056</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -874,19 +854,9 @@
           <t>2002-07-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2002-07-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 19676-2024 artfynd.xlsx
+++ b/artfynd/A 19676-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>90428543</v>
       </c>
       <c r="B2" t="n">
-        <v>105428</v>
+        <v>105440</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Annica Nordin, Ingvar Nordin</t>
+          <t>Ingvar Nordin, Annica Nordin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -789,7 +789,7 @@
         <v>90428547</v>
       </c>
       <c r="B3" t="n">
-        <v>107061</v>
+        <v>107075</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Annica Nordin, Ingvar Nordin</t>
+          <t>Ingvar Nordin, Annica Nordin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 19676-2024 artfynd.xlsx
+++ b/artfynd/A 19676-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>90428543</v>
       </c>
       <c r="B2" t="n">
-        <v>105440</v>
+        <v>105449</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ingvar Nordin, Annica Nordin</t>
+          <t>Annica Nordin, Ingvar Nordin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -789,7 +789,7 @@
         <v>90428547</v>
       </c>
       <c r="B3" t="n">
-        <v>107075</v>
+        <v>107084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ingvar Nordin, Annica Nordin</t>
+          <t>Annica Nordin, Ingvar Nordin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 19676-2024 artfynd.xlsx
+++ b/artfynd/A 19676-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>90428543</v>
       </c>
       <c r="B2" t="n">
-        <v>105449</v>
+        <v>105461</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>90428547</v>
       </c>
       <c r="B3" t="n">
-        <v>107084</v>
+        <v>107096</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 19676-2024 artfynd.xlsx
+++ b/artfynd/A 19676-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>90428543</v>
       </c>
       <c r="B2" t="n">
-        <v>105461</v>
+        <v>105470</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>90428547</v>
       </c>
       <c r="B3" t="n">
-        <v>107096</v>
+        <v>107105</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 19676-2024 artfynd.xlsx
+++ b/artfynd/A 19676-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>90428543</v>
       </c>
       <c r="B2" t="n">
-        <v>105470</v>
+        <v>105473</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>90428547</v>
       </c>
       <c r="B3" t="n">
-        <v>107105</v>
+        <v>107110</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 19676-2024 artfynd.xlsx
+++ b/artfynd/A 19676-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>90428543</v>
       </c>
       <c r="B2" t="n">
-        <v>105473</v>
+        <v>105501</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>90428547</v>
       </c>
       <c r="B3" t="n">
-        <v>107110</v>
+        <v>107138</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 19676-2024 artfynd.xlsx
+++ b/artfynd/A 19676-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>90428543</v>
       </c>
       <c r="B2" t="n">
-        <v>105501</v>
+        <v>105507</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>90428547</v>
       </c>
       <c r="B3" t="n">
-        <v>107138</v>
+        <v>107144</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 19676-2024 artfynd.xlsx
+++ b/artfynd/A 19676-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>90428543</v>
       </c>
       <c r="B2" t="n">
-        <v>105528</v>
+        <v>105533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>90428547</v>
       </c>
       <c r="B3" t="n">
-        <v>107166</v>
+        <v>107171</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 19676-2024 artfynd.xlsx
+++ b/artfynd/A 19676-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>90428543</v>
+        <v>412054</v>
       </c>
       <c r="B2" t="n">
-        <v>105533</v>
+        <v>80333</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221101</v>
+        <v>956</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Gråblå skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Leptogium cyanescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Rabenh.) Körb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mellan Kristinedal och Nytorp, intill vägen, Boh</t>
+          <t>Gustavsbergs NR, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>319939</v>
+        <v>320008</v>
       </c>
       <c r="R2" t="n">
-        <v>6469056</v>
+        <v>6469172</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,17 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2002-07-18</t>
+          <t>2004-08-19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2002-07-18</t>
+          <t>2004-08-19</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Bohusläns flora - 2011.</t>
+          <t>På översilade klipphällar intill Bodeleån strax nedströms vägen.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,32 +764,28 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Lund</t>
+          <t>Översilade klipphällar.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Evastina Blomgren</t>
+          <t>Andreas Malmqvist</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Annica Nordin, Ingvar Nordin</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Bohusläns Flora 2011</t>
-        </is>
-      </c>
+          <t>Andreas Malmqvist</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>90428547</v>
+        <v>1877656</v>
       </c>
       <c r="B3" t="n">
-        <v>107171</v>
+        <v>80300</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,37 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220015</v>
+        <v>6441</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hässleklocka</t>
+          <t>Slanklav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Campanula latifolia</t>
+          <t>Collema flaccidum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mellan Kristinedal och Nytorp, intill vägen, Boh</t>
+          <t>Gustavsbergs NR, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>319939</v>
+        <v>320008</v>
       </c>
       <c r="R3" t="n">
-        <v>6469056</v>
+        <v>6469172</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -851,17 +847,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2002-07-18</t>
+          <t>2004-08-19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2002-07-18</t>
+          <t>2004-08-19</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Bohusläns flora - 2011.</t>
+          <t>På översilade klipphällar intill Bodeleån strax nedströms vägen.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -875,25 +871,1291 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Lund</t>
+          <t>Översilade klipphällar.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Evastina Blomgren</t>
+          <t>Andreas Malmqvist</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Annica Nordin, Ingvar Nordin</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Bohusläns Flora 2011</t>
-        </is>
-      </c>
+          <t>Andreas Malmqvist</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>75651546</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bodeleån, Bodele, Uddevalla, Boh</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>320007</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6469015</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2019-01-10</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2019-01-10</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Rune Hixén</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Rune Hixén</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>77582236</v>
+      </c>
+      <c r="B5" t="n">
+        <v>107609</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219686</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vätteros</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lathraea squamaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bodeleån, Bodele, Uddevalla, Boh</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>320007</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6469015</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2019-05-06</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2019-05-06</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Rune Hixén</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Rune Hixén</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>116169553</v>
+      </c>
+      <c r="B6" t="n">
+        <v>107609</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219686</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vätteros</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lathraea squamaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Fallet, Bodeleån, Bodele, Uddevalla, Boh</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>319943</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6469144</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-04-22</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-04-22</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Rune Hixén</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Rune Hixén</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>67630243</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99141</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bodeleån, Bodele, Uddevalla, Boh</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>320007</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6469015</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2017-09-20</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2017-09-20</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Rune Hixén</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Rune Hixén</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>106041367</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99141</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Fallet, Bodeleån, Bodele, Uddevalla, Boh</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>319943</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6469144</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-01-17</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-01-17</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Rune Hixén</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Rune Hixén</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>123595258</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101897</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220075</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Gullpudra</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Chrysosplenium alternifolium</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Fallet, Bodeleån, Bodele, Uddevalla, Boh</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>319943</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6469144</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Rune Hixén</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Rune Hixén</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>78852420</v>
+      </c>
+      <c r="B10" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bodeleån, Bodele, Uddevalla, Boh</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>320007</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6469015</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2019-07-10</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>19:04</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2019-07-10</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Rune Hixén</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Rune Hixén</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>102569169</v>
+      </c>
+      <c r="B11" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Gustavsberg, vägkant ca 180m O om Kristinedal, Boh</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>319693</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6469211</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2022-07-30</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2022-07-30</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Bo Eriksson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Bo Eriksson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>132807881</v>
+      </c>
+      <c r="B12" t="n">
+        <v>104197</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221987</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Skogsbingel</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Mercurialis perennis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Fallet, Bodeleån, Bodele, Uddevalla, Boh</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>319943</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6469144</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Rune Hixén</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Rune Hixén</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>116169383</v>
+      </c>
+      <c r="B13" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Fallet, Bodeleån, Bodele, Uddevalla, Boh</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>319943</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6469144</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-04-22</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-04-22</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Rune Hixén</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Rune Hixén</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>132234188</v>
+      </c>
+      <c r="B14" t="n">
+        <v>101324</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222782</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vitsippa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Anemone nemorosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Fallet, Bodeleån, Bodele, Uddevalla, Boh</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>319943</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6469144</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Rune Hixén</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Rune Hixén</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 19676-2024 artfynd.xlsx
+++ b/artfynd/A 19676-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/412054</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1877656</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75651546</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1124,6 +1144,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77582236</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1236,6 +1261,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116169553</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1354,6 +1384,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67630243</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1478,6 +1513,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106041367</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1594,6 +1634,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123595258</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1706,6 +1751,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78852420</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1808,6 +1858,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102569169</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1924,6 +1979,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132807881</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2040,6 +2100,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116169383</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2156,8 +2221,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132234188</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>